--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 мррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 мррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78A70BD-CF53-42D2-AFA8-58E68507CE04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A9CC60-56B5-4753-9B1E-638549065F7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5475,7 +5475,10 @@
         <f>SUM(Z6:Z494)</f>
         <v>2610.34</v>
       </c>
-      <c r="AA5" s="1"/>
+      <c r="AA5" s="4">
+        <f>SUM(AA6:AA494)</f>
+        <v>497.56059999999991</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
@@ -5576,7 +5579,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="1"/>
+      <c r="AA6" s="1">
+        <f>P6*G6</f>
+        <v>0.43339999999999995</v>
+      </c>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
@@ -5677,7 +5683,10 @@
         <f t="shared" ref="Z7:Z70" si="6">G7*R7</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="1"/>
+      <c r="AA7" s="1">
+        <f t="shared" ref="AA7:AA70" si="7">P7*G7</f>
+        <v>4.6399999999999997</v>
+      </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
@@ -5778,7 +5787,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA8" s="1"/>
+      <c r="AA8" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1848000000000001</v>
+      </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -5850,7 +5862,7 @@
         <v>16.2</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" ref="Q9:Q31" si="7">15*P9-O9-F9</f>
+        <f t="shared" ref="Q9:Q31" si="8">15*P9-O9-F9</f>
         <v>38</v>
       </c>
       <c r="R9" s="5">
@@ -5880,7 +5892,10 @@
         <f t="shared" si="6"/>
         <v>9.5</v>
       </c>
-      <c r="AA9" s="1"/>
+      <c r="AA9" s="1">
+        <f t="shared" si="7"/>
+        <v>4.05</v>
+      </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
@@ -5952,7 +5967,7 @@
         <v>22.943199999999997</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>97.908999999999963</v>
       </c>
       <c r="R10" s="5">
@@ -5982,7 +5997,10 @@
         <f t="shared" si="6"/>
         <v>98</v>
       </c>
-      <c r="AA10" s="1"/>
+      <c r="AA10" s="1">
+        <f t="shared" si="7"/>
+        <v>22.943199999999997</v>
+      </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
@@ -6083,7 +6101,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="1"/>
+      <c r="AA11" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2214</v>
+      </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
@@ -6182,7 +6203,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="1"/>
+      <c r="AA12" s="1">
+        <f t="shared" si="7"/>
+        <v>5.9462000000000002</v>
+      </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
@@ -6254,7 +6278,7 @@
         <v>27.268599999999999</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50.462999999999994</v>
       </c>
       <c r="R13" s="5">
@@ -6287,7 +6311,10 @@
         <f t="shared" si="6"/>
         <v>120</v>
       </c>
-      <c r="AA13" s="1"/>
+      <c r="AA13" s="1">
+        <f t="shared" si="7"/>
+        <v>27.268599999999999</v>
+      </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
@@ -6359,7 +6386,7 @@
         <v>15.4</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
       <c r="R14" s="5">
@@ -6392,7 +6419,10 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="AA14" s="1"/>
+      <c r="AA14" s="1">
+        <f t="shared" si="7"/>
+        <v>3.85</v>
+      </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -6489,7 +6519,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="1"/>
+      <c r="AA15" s="1">
+        <f t="shared" si="7"/>
+        <v>7.9296000000000006</v>
+      </c>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
@@ -6561,7 +6594,7 @@
         <v>20.2</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="R16" s="5">
@@ -6594,7 +6627,10 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="AA16" s="1"/>
+      <c r="AA16" s="1">
+        <f t="shared" si="7"/>
+        <v>5.05</v>
+      </c>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
@@ -6695,7 +6731,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="1"/>
+      <c r="AA17" s="1">
+        <f t="shared" si="7"/>
+        <v>2.16</v>
+      </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
@@ -6767,7 +6806,7 @@
         <v>21.8306</v>
       </c>
       <c r="Q18" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162.589</v>
       </c>
       <c r="R18" s="5">
@@ -6800,7 +6839,10 @@
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
-      <c r="AA18" s="1"/>
+      <c r="AA18" s="1">
+        <f t="shared" si="7"/>
+        <v>21.8306</v>
+      </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -6895,7 +6937,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="1"/>
+      <c r="AA19" s="1">
+        <f t="shared" si="7"/>
+        <v>0.60439999999999994</v>
+      </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
@@ -6996,7 +7041,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="1"/>
+      <c r="AA20" s="1">
+        <f t="shared" si="7"/>
+        <v>2.8000000000000003</v>
+      </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
@@ -7068,7 +7116,7 @@
         <v>13.8462</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17.634999999999991</v>
       </c>
       <c r="R21" s="5">
@@ -7098,7 +7146,10 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="AA21" s="1"/>
+      <c r="AA21" s="1">
+        <f t="shared" si="7"/>
+        <v>13.8462</v>
+      </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
@@ -7200,7 +7251,10 @@
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="AA22" s="1"/>
+      <c r="AA22" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
@@ -7301,7 +7355,10 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="AA23" s="1"/>
+      <c r="AA23" s="1">
+        <f t="shared" si="7"/>
+        <v>2.0428000000000002</v>
+      </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
@@ -7406,7 +7463,10 @@
         <f t="shared" si="6"/>
         <v>120</v>
       </c>
-      <c r="AA24" s="1"/>
+      <c r="AA24" s="1">
+        <f t="shared" si="7"/>
+        <v>10.5684</v>
+      </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
@@ -7507,7 +7567,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA25" s="1"/>
+      <c r="AA25" s="1">
+        <f t="shared" si="7"/>
+        <v>0.88200000000000001</v>
+      </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
@@ -7606,7 +7669,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <f t="shared" si="7"/>
+        <v>0.504</v>
+      </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
@@ -7707,7 +7773,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <f t="shared" si="7"/>
+        <v>0.72</v>
+      </c>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
@@ -7808,7 +7877,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="1"/>
+      <c r="AA28" s="1">
+        <f t="shared" si="7"/>
+        <v>5.7783999999999995</v>
+      </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
@@ -7907,7 +7979,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <f t="shared" si="7"/>
+        <v>3.12</v>
+      </c>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
@@ -7979,11 +8054,11 @@
         <v>35</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>151</v>
       </c>
       <c r="R30" s="5">
-        <f t="shared" ref="R30:R31" si="8">S30</f>
+        <f t="shared" ref="R30:R31" si="9">S30</f>
         <v>250</v>
       </c>
       <c r="S30" s="17">
@@ -8012,7 +8087,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AA30" s="1"/>
+      <c r="AA30" s="1">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
@@ -8084,11 +8162,11 @@
         <v>39.6</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>205</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="S31" s="17">
@@ -8117,7 +8195,10 @@
         <f t="shared" si="6"/>
         <v>120</v>
       </c>
-      <c r="AA31" s="1"/>
+      <c r="AA31" s="1">
+        <f t="shared" si="7"/>
+        <v>15.840000000000002</v>
+      </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
@@ -8218,7 +8299,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
@@ -8319,7 +8403,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <f t="shared" si="7"/>
+        <v>7.6383999999999999</v>
+      </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
@@ -8418,7 +8505,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <f t="shared" si="7"/>
+        <v>1.0569999999999999</v>
+      </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
@@ -8490,7 +8580,7 @@
         <v>7.3105999999999991</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" ref="Q35:Q40" si="9">15*P35-O35-F35</f>
+        <f t="shared" ref="Q35:Q40" si="10">15*P35-O35-F35</f>
         <v>37.611999999999995</v>
       </c>
       <c r="R35" s="5">
@@ -8520,7 +8610,10 @@
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <f t="shared" si="7"/>
+        <v>7.3105999999999991</v>
+      </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
@@ -8621,7 +8714,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2730000000000001</v>
+      </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
@@ -8722,7 +8818,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <f t="shared" si="7"/>
+        <v>5.3999999999999995</v>
+      </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
@@ -8779,7 +8878,7 @@
         <v>4</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="10">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
         <v>0.66000000000000014</v>
       </c>
       <c r="M38" s="1"/>
@@ -8788,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P69" si="11">E38/5</f>
+        <f t="shared" ref="P38:P69" si="12">E38/5</f>
         <v>0.93200000000000005</v>
       </c>
       <c r="Q38" s="5"/>
@@ -8802,7 +8901,7 @@
         <v>61.740343347639481</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="12">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="13">(F38+O38)/P38</f>
         <v>61.740343347639481</v>
       </c>
       <c r="V38" s="1">
@@ -8821,7 +8920,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <f t="shared" si="7"/>
+        <v>0.93200000000000005</v>
+      </c>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
@@ -8874,7 +8976,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M39" s="1"/>
@@ -8883,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q39" s="5"/>
@@ -8897,7 +8999,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U39" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V39" s="1">
@@ -8916,7 +9018,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA39" s="1"/>
+      <c r="AA39" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
@@ -8975,7 +9080,7 @@
         <v>501</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-135</v>
       </c>
       <c r="M40" s="1"/>
@@ -8984,11 +9089,11 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>73.2</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>540</v>
       </c>
       <c r="R40" s="5">
@@ -9001,7 +9106,7 @@
         <v>15</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.6229508196721305</v>
       </c>
       <c r="V40" s="1">
@@ -9018,7 +9123,10 @@
         <f t="shared" si="6"/>
         <v>189</v>
       </c>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <f t="shared" si="7"/>
+        <v>25.62</v>
+      </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
@@ -9077,7 +9185,7 @@
         <v>51</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4</v>
       </c>
       <c r="M41" s="10"/>
@@ -9086,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.4</v>
       </c>
       <c r="Q41" s="12"/>
@@ -9100,7 +9208,7 @@
         <v>-1.1702127659574468</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.1702127659574468</v>
       </c>
       <c r="V41" s="10">
@@ -9119,7 +9227,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
@@ -9178,7 +9289,7 @@
         <v>79</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-2</v>
       </c>
       <c r="M42" s="1"/>
@@ -9187,11 +9298,11 @@
         <v>51</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.4</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" ref="Q42:Q45" si="13">15*P42-O42-F42</f>
+        <f t="shared" ref="Q42:Q45" si="14">15*P42-O42-F42</f>
         <v>38</v>
       </c>
       <c r="R42" s="5">
@@ -9204,7 +9315,7 @@
         <v>15</v>
       </c>
       <c r="U42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.532467532467532</v>
       </c>
       <c r="V42" s="1">
@@ -9221,7 +9332,10 @@
         <f t="shared" si="6"/>
         <v>15.579999999999998</v>
       </c>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <f t="shared" si="7"/>
+        <v>6.3140000000000001</v>
+      </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
@@ -9280,7 +9394,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-6</v>
       </c>
       <c r="M43" s="1"/>
@@ -9289,7 +9403,7 @@
         <v>69</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="Q43" s="5"/>
@@ -9305,7 +9419,7 @@
         <v>32.333333333333336</v>
       </c>
       <c r="U43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22.333333333333332</v>
       </c>
       <c r="V43" s="1">
@@ -9322,7 +9436,10 @@
         <f t="shared" si="6"/>
         <v>10.799999999999999</v>
       </c>
-      <c r="AA43" s="1"/>
+      <c r="AA43" s="1">
+        <f t="shared" si="7"/>
+        <v>1.08</v>
+      </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
@@ -9381,7 +9498,7 @@
         <v>57</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-16</v>
       </c>
       <c r="M44" s="1"/>
@@ -9390,7 +9507,7 @@
         <v>18</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="Q44" s="5">
@@ -9409,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="U44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.1463414634146343</v>
       </c>
       <c r="V44" s="1">
@@ -9426,7 +9543,10 @@
         <f t="shared" si="6"/>
         <v>42.9</v>
       </c>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <f t="shared" si="7"/>
+        <v>2.706</v>
+      </c>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
@@ -9485,7 +9605,7 @@
         <v>56</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7</v>
       </c>
       <c r="M45" s="1"/>
@@ -9494,11 +9614,11 @@
         <v>0</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="Q45" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>56</v>
       </c>
       <c r="R45" s="5">
@@ -9513,7 +9633,7 @@
         <v>19.489795918367346</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.2857142857142847</v>
       </c>
       <c r="V45" s="1">
@@ -9530,7 +9650,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <f t="shared" si="7"/>
+        <v>3.9200000000000004</v>
+      </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
@@ -9583,7 +9706,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M46" s="1"/>
@@ -9592,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q46" s="5"/>
@@ -9606,7 +9729,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U46" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V46" s="1">
@@ -9623,7 +9746,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
@@ -9680,7 +9806,7 @@
         <v>38</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-30</v>
       </c>
       <c r="M47" s="1"/>
@@ -9689,7 +9815,7 @@
         <v>97</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.6</v>
       </c>
       <c r="Q47" s="5"/>
@@ -9703,7 +9829,7 @@
         <v>81.293125000000003</v>
       </c>
       <c r="U47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>81.293125000000003</v>
       </c>
       <c r="V47" s="1">
@@ -9720,7 +9846,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <f t="shared" si="7"/>
+        <v>1.6</v>
+      </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
@@ -9779,7 +9908,7 @@
         <v>37</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-22</v>
       </c>
       <c r="M48" s="1"/>
@@ -9788,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="Q48" s="5"/>
@@ -9802,7 +9931,7 @@
         <v>77</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>77</v>
       </c>
       <c r="V48" s="1">
@@ -9821,7 +9950,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2000000000000002</v>
+      </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -9880,7 +10012,7 @@
         <v>6</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.4999999999999964E-2</v>
       </c>
       <c r="M49" s="1"/>
@@ -9889,7 +10021,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.2170000000000001</v>
       </c>
       <c r="Q49" s="5"/>
@@ -9903,7 +10035,7 @@
         <v>30.870994248151188</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.870994248151188</v>
       </c>
       <c r="V49" s="1">
@@ -9922,7 +10054,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2170000000000001</v>
+      </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
@@ -9981,7 +10116,7 @@
         <v>2.5</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.49000000000000021</v>
       </c>
       <c r="M50" s="1"/>
@@ -9990,7 +10125,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.59800000000000009</v>
       </c>
       <c r="Q50" s="5"/>
@@ -10004,7 +10139,7 @@
         <v>186.62207357859529</v>
       </c>
       <c r="U50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>186.62207357859529</v>
       </c>
       <c r="V50" s="1">
@@ -10023,7 +10158,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <f t="shared" si="7"/>
+        <v>0.59800000000000009</v>
+      </c>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
@@ -10074,7 +10212,7 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M51" s="10"/>
@@ -10083,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q51" s="12"/>
@@ -10097,7 +10235,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U51" s="10" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V51" s="10">
@@ -10114,7 +10252,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
@@ -10173,7 +10314,7 @@
         <v>51</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-5</v>
       </c>
       <c r="M52" s="1"/>
@@ -10182,11 +10323,11 @@
         <v>0</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="Q52" s="5">
-        <f t="shared" ref="Q52:Q57" si="14">15*P52-O52-F52</f>
+        <f t="shared" ref="Q52:Q57" si="15">15*P52-O52-F52</f>
         <v>12</v>
       </c>
       <c r="R52" s="5">
@@ -10199,7 +10340,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="U52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.695652173913045</v>
       </c>
       <c r="V52" s="1">
@@ -10216,7 +10357,10 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="AA52" s="1"/>
+      <c r="AA52" s="1">
+        <f t="shared" si="7"/>
+        <v>2.2999999999999998</v>
+      </c>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
@@ -10273,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1</v>
       </c>
       <c r="M53" s="1"/>
@@ -10282,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q53" s="5"/>
@@ -10296,7 +10440,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U53" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V53" s="1">
@@ -10315,7 +10459,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="1"/>
+      <c r="AA53" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
@@ -10368,7 +10515,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M54" s="1"/>
@@ -10377,7 +10524,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q54" s="5"/>
@@ -10391,7 +10538,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U54" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V54" s="1">
@@ -10410,7 +10557,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="1"/>
+      <c r="AA54" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
@@ -10469,7 +10619,7 @@
         <v>26</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-5</v>
       </c>
       <c r="M55" s="1"/>
@@ -10478,7 +10628,7 @@
         <v>21</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.2</v>
       </c>
       <c r="Q55" s="5"/>
@@ -10492,7 +10642,7 @@
         <v>18.095238095238095</v>
       </c>
       <c r="U55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18.095238095238095</v>
       </c>
       <c r="V55" s="1">
@@ -10511,7 +10661,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="1"/>
+      <c r="AA55" s="1">
+        <f t="shared" si="7"/>
+        <v>1.26</v>
+      </c>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
@@ -10568,7 +10721,7 @@
         <v>707</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-150</v>
       </c>
       <c r="M56" s="1"/>
@@ -10577,11 +10730,11 @@
         <v>500</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>111.4</v>
       </c>
       <c r="Q56" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>831</v>
       </c>
       <c r="R56" s="5">
@@ -10594,7 +10747,7 @@
         <v>15</v>
       </c>
       <c r="U56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.5403949730700175</v>
       </c>
       <c r="V56" s="1">
@@ -10611,7 +10764,10 @@
         <f t="shared" si="6"/>
         <v>340.71</v>
       </c>
-      <c r="AA56" s="1"/>
+      <c r="AA56" s="1">
+        <f t="shared" si="7"/>
+        <v>45.673999999999999</v>
+      </c>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
@@ -10670,7 +10826,7 @@
         <v>36</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.36899999999999977</v>
       </c>
       <c r="M57" s="1"/>
@@ -10679,11 +10835,11 @@
         <v>43</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.1261999999999999</v>
       </c>
       <c r="Q57" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.310000000000002</v>
       </c>
       <c r="R57" s="5">
@@ -10696,7 +10852,7 @@
         <v>14.956498554629396</v>
       </c>
       <c r="U57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.57093542140271</v>
       </c>
       <c r="V57" s="1">
@@ -10713,7 +10869,10 @@
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="AA57" s="1"/>
+      <c r="AA57" s="1">
+        <f t="shared" si="7"/>
+        <v>7.1261999999999999</v>
+      </c>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
@@ -10772,7 +10931,7 @@
         <v>115</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-37</v>
       </c>
       <c r="M58" s="1"/>
@@ -10781,7 +10940,7 @@
         <v>84</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.6</v>
       </c>
       <c r="Q58" s="5"/>
@@ -10795,7 +10954,7 @@
         <v>20.641025641025642</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20.641025641025642</v>
       </c>
       <c r="V58" s="1">
@@ -10812,7 +10971,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="1"/>
+      <c r="AA58" s="1">
+        <f t="shared" si="7"/>
+        <v>5.46</v>
+      </c>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
@@ -10865,7 +11027,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M59" s="1"/>
@@ -10874,7 +11036,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q59" s="5"/>
@@ -10888,7 +11050,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U59" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V59" s="1">
@@ -10905,7 +11067,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="1"/>
+      <c r="AA59" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
@@ -10964,7 +11129,7 @@
         <v>252</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-34</v>
       </c>
       <c r="M60" s="1"/>
@@ -10973,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>43.6</v>
       </c>
       <c r="Q60" s="5"/>
@@ -10987,7 +11152,7 @@
         <v>17.660550458715594</v>
       </c>
       <c r="U60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17.660550458715594</v>
       </c>
       <c r="V60" s="1">
@@ -11006,7 +11171,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA60" s="1"/>
+      <c r="AA60" s="1">
+        <f t="shared" si="7"/>
+        <v>17.876000000000001</v>
+      </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
@@ -11061,7 +11229,7 @@
         <v>6</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-2.9129999999999998</v>
       </c>
       <c r="M61" s="1"/>
@@ -11070,7 +11238,7 @@
         <v>16</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.61740000000000006</v>
       </c>
       <c r="Q61" s="5"/>
@@ -11084,7 +11252,7 @@
         <v>25.915127955944278</v>
       </c>
       <c r="U61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>25.915127955944278</v>
       </c>
       <c r="V61" s="1">
@@ -11101,7 +11269,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA61" s="1"/>
+      <c r="AA61" s="1">
+        <f t="shared" si="7"/>
+        <v>0.61740000000000006</v>
+      </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
@@ -11160,7 +11331,7 @@
         <v>58</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7</v>
       </c>
       <c r="M62" s="1"/>
@@ -11169,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.199999999999999</v>
       </c>
       <c r="Q62" s="5"/>
@@ -11183,7 +11354,7 @@
         <v>21.862745098039216</v>
       </c>
       <c r="U62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.862745098039216</v>
       </c>
       <c r="V62" s="1">
@@ -11202,7 +11373,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA62" s="1"/>
+      <c r="AA62" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0599999999999996</v>
+      </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
@@ -11255,14 +11429,14 @@
         <v>2</v>
       </c>
       <c r="L63" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="Q63" s="12"/>
@@ -11276,7 +11450,7 @@
         <v>-5</v>
       </c>
       <c r="U63" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5</v>
       </c>
       <c r="V63" s="10">
@@ -11293,7 +11467,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA63" s="1"/>
+      <c r="AA63" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
@@ -11352,7 +11529,7 @@
         <v>69</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-23</v>
       </c>
       <c r="M64" s="1"/>
@@ -11361,11 +11538,11 @@
         <v>95</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="Q64" s="5">
-        <f t="shared" ref="Q64" si="15">15*P64-O64-F64</f>
+        <f t="shared" ref="Q64" si="16">15*P64-O64-F64</f>
         <v>40</v>
       </c>
       <c r="R64" s="5">
@@ -11378,7 +11555,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="U64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.652173913043478</v>
       </c>
       <c r="V64" s="1">
@@ -11395,7 +11572,10 @@
         <f t="shared" si="6"/>
         <v>7.1999999999999993</v>
       </c>
-      <c r="AA64" s="1"/>
+      <c r="AA64" s="1">
+        <f t="shared" si="7"/>
+        <v>1.6559999999999999</v>
+      </c>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -11448,7 +11628,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M65" s="1"/>
@@ -11457,7 +11637,7 @@
         <v>0</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q65" s="5"/>
@@ -11471,7 +11651,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U65" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V65" s="1">
@@ -11490,7 +11670,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA65" s="1"/>
+      <c r="AA65" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -11537,7 +11720,7 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M66" s="10"/>
@@ -11546,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q66" s="12"/>
@@ -11560,7 +11743,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U66" s="10" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V66" s="10">
@@ -11579,7 +11762,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA66" s="1"/>
+      <c r="AA66" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -11638,7 +11824,7 @@
         <v>465</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-109</v>
       </c>
       <c r="M67" s="1"/>
@@ -11647,7 +11833,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>71.2</v>
       </c>
       <c r="Q67" s="5">
@@ -11664,7 +11850,7 @@
         <v>15</v>
       </c>
       <c r="U67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.0898876404494384</v>
       </c>
       <c r="V67" s="1">
@@ -11681,7 +11867,10 @@
         <f t="shared" si="6"/>
         <v>172.2</v>
       </c>
-      <c r="AA67" s="1"/>
+      <c r="AA67" s="1">
+        <f t="shared" si="7"/>
+        <v>24.919999999999998</v>
+      </c>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
@@ -11728,7 +11917,7 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M68" s="10"/>
@@ -11737,7 +11926,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q68" s="12"/>
@@ -11751,7 +11940,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U68" s="10" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" s="10">
@@ -11770,7 +11959,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AA68" s="1"/>
+      <c r="AA68" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
@@ -11827,7 +12019,7 @@
         <v>31</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-6.9269999999999996</v>
       </c>
       <c r="M69" s="1"/>
@@ -11836,11 +12028,11 @@
         <v>0</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.8146000000000004</v>
       </c>
       <c r="Q69" s="5">
-        <f t="shared" ref="Q69:Q75" si="16">15*P69-O69-F69</f>
+        <f t="shared" ref="Q69:Q75" si="17">15*P69-O69-F69</f>
         <v>6.0750000000000028</v>
       </c>
       <c r="R69" s="5">
@@ -11853,7 +12045,7 @@
         <v>14.984422381921656</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.738212935654053</v>
       </c>
       <c r="V69" s="1">
@@ -11870,7 +12062,10 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="AA69" s="1"/>
+      <c r="AA69" s="1">
+        <f t="shared" si="7"/>
+        <v>4.8146000000000004</v>
+      </c>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
@@ -11929,7 +12124,7 @@
         <v>114.3</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="17">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
         <v>-5.0690000000000026</v>
       </c>
       <c r="M70" s="1"/>
@@ -11938,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="1">
-        <f t="shared" ref="P70:P106" si="18">E70/5</f>
+        <f t="shared" ref="P70:P106" si="19">E70/5</f>
         <v>21.8462</v>
       </c>
       <c r="Q70" s="5">
@@ -11955,7 +12150,7 @@
         <v>13.985910593146635</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U106" si="19">(F70+O70)/P70</f>
+        <f t="shared" ref="U70:U106" si="20">(F70+O70)/P70</f>
         <v>6.4788841995404232</v>
       </c>
       <c r="V70" s="1">
@@ -11972,7 +12167,10 @@
         <f t="shared" si="6"/>
         <v>164</v>
       </c>
-      <c r="AA70" s="1"/>
+      <c r="AA70" s="1">
+        <f t="shared" si="7"/>
+        <v>21.8462</v>
+      </c>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
@@ -12029,7 +12227,7 @@
         <v>473</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-103</v>
       </c>
       <c r="M71" s="1"/>
@@ -12038,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74</v>
       </c>
       <c r="Q71" s="5">
@@ -12046,16 +12244,16 @@
         <v>605</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" ref="R71:R106" si="20">ROUND(Q71,0)</f>
+        <f t="shared" ref="R71:R106" si="21">ROUND(Q71,0)</f>
         <v>605</v>
       </c>
       <c r="S71" s="17"/>
       <c r="T71" s="1">
-        <f t="shared" ref="T71:T106" si="21">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="T71:T106" si="22">(F71+O71+R71)/P71</f>
         <v>11</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.8243243243243241</v>
       </c>
       <c r="V71" s="1">
@@ -12069,10 +12267,13 @@
       </c>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1">
-        <f t="shared" ref="Z71:Z106" si="22">G71*R71</f>
+        <f t="shared" ref="Z71:Z106" si="23">G71*R71</f>
         <v>211.75</v>
       </c>
-      <c r="AA71" s="1"/>
+      <c r="AA71" s="1">
+        <f t="shared" ref="AA71:AA106" si="24">P71*G71</f>
+        <v>25.9</v>
+      </c>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
@@ -12131,7 +12332,7 @@
         <v>75</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-46</v>
       </c>
       <c r="M72" s="1"/>
@@ -12140,21 +12341,21 @@
         <v>137</v>
       </c>
       <c r="P72" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.8</v>
       </c>
       <c r="Q72" s="5"/>
       <c r="R72" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S72" s="17"/>
       <c r="T72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>43.793103448275865</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>43.793103448275865</v>
       </c>
       <c r="V72" s="1">
@@ -12168,10 +12369,13 @@
       </c>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA72" s="1"/>
+      <c r="AA72" s="1">
+        <f t="shared" si="24"/>
+        <v>1.74</v>
+      </c>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
@@ -12230,7 +12434,7 @@
         <v>11</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-2</v>
       </c>
       <c r="M73" s="1"/>
@@ -12239,21 +12443,21 @@
         <v>0</v>
       </c>
       <c r="P73" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.8</v>
       </c>
       <c r="Q73" s="5"/>
       <c r="R73" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S73" s="17"/>
       <c r="T73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>42.777777777777779</v>
       </c>
       <c r="U73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>42.777777777777779</v>
       </c>
       <c r="V73" s="1">
@@ -12269,10 +12473,13 @@
         <v>37</v>
       </c>
       <c r="Z73" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA73" s="1"/>
+      <c r="AA73" s="1">
+        <f t="shared" si="24"/>
+        <v>0.54</v>
+      </c>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
@@ -12331,7 +12538,7 @@
         <v>158</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-16</v>
       </c>
       <c r="M74" s="1"/>
@@ -12340,24 +12547,24 @@
         <v>34</v>
       </c>
       <c r="P74" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.4</v>
       </c>
       <c r="Q74" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>106</v>
       </c>
       <c r="S74" s="17"/>
       <c r="T74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="U74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.267605633802818</v>
       </c>
       <c r="V74" s="1">
@@ -12371,10 +12578,13 @@
       </c>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>29.680000000000003</v>
       </c>
-      <c r="AA74" s="1"/>
+      <c r="AA74" s="1">
+        <f t="shared" si="24"/>
+        <v>7.952</v>
+      </c>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
@@ -12431,7 +12641,7 @@
         <v>218</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-22</v>
       </c>
       <c r="M75" s="1"/>
@@ -12440,24 +12650,24 @@
         <v>0</v>
       </c>
       <c r="P75" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>39.200000000000003</v>
       </c>
       <c r="Q75" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>282</v>
       </c>
       <c r="R75" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>282</v>
       </c>
       <c r="S75" s="17"/>
       <c r="T75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14.999999999999998</v>
       </c>
       <c r="U75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.8061224489795915</v>
       </c>
       <c r="V75" s="1">
@@ -12471,10 +12681,13 @@
       </c>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78.960000000000008</v>
       </c>
-      <c r="AA75" s="1"/>
+      <c r="AA75" s="1">
+        <f t="shared" si="24"/>
+        <v>10.976000000000003</v>
+      </c>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
@@ -12533,7 +12746,7 @@
         <v>192</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-167</v>
       </c>
       <c r="M76" s="1"/>
@@ -12542,21 +12755,21 @@
         <v>5</v>
       </c>
       <c r="P76" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="Q76" s="5"/>
       <c r="R76" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S76" s="17"/>
       <c r="T76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>88</v>
       </c>
       <c r="U76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>88</v>
       </c>
       <c r="V76" s="1">
@@ -12570,10 +12783,13 @@
       </c>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA76" s="1"/>
+      <c r="AA76" s="1">
+        <f t="shared" si="24"/>
+        <v>1.4000000000000001</v>
+      </c>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
@@ -12632,7 +12848,7 @@
         <v>285</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-173</v>
       </c>
       <c r="M77" s="1"/>
@@ -12641,21 +12857,21 @@
         <v>0</v>
       </c>
       <c r="P77" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>22.4</v>
       </c>
       <c r="Q77" s="5"/>
       <c r="R77" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S77" s="17"/>
       <c r="T77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30.178571428571431</v>
       </c>
       <c r="U77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30.178571428571431</v>
       </c>
       <c r="V77" s="1">
@@ -12669,10 +12885,13 @@
       </c>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA77" s="1"/>
+      <c r="AA77" s="1">
+        <f t="shared" si="24"/>
+        <v>8.9599999999999991</v>
+      </c>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
@@ -12729,7 +12948,7 @@
         <v>11.1</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.79499999999999993</v>
       </c>
       <c r="M78" s="1"/>
@@ -12738,21 +12957,21 @@
         <v>0</v>
       </c>
       <c r="P78" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.379</v>
       </c>
       <c r="Q78" s="5"/>
       <c r="R78" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S78" s="17"/>
       <c r="T78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36.140395124001678</v>
       </c>
       <c r="U78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>36.140395124001678</v>
       </c>
       <c r="V78" s="1">
@@ -12766,10 +12985,13 @@
       </c>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA78" s="1"/>
+      <c r="AA78" s="1">
+        <f t="shared" si="24"/>
+        <v>2.379</v>
+      </c>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
@@ -12822,7 +13044,7 @@
         <v>5</v>
       </c>
       <c r="L79" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-5</v>
       </c>
       <c r="M79" s="10"/>
@@ -12831,21 +13053,21 @@
         <v>0</v>
       </c>
       <c r="P79" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q79" s="12"/>
       <c r="R79" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S79" s="17"/>
       <c r="T79" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" s="10">
@@ -12859,10 +13081,13 @@
       </c>
       <c r="Y79" s="10"/>
       <c r="Z79" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA79" s="1"/>
+      <c r="AA79" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
@@ -12921,7 +13146,7 @@
         <v>12</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M80" s="1"/>
@@ -12930,21 +13155,21 @@
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.4</v>
       </c>
       <c r="Q80" s="5"/>
       <c r="R80" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S80" s="17"/>
       <c r="T80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>82.083333333333343</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>82.083333333333343</v>
       </c>
       <c r="V80" s="1">
@@ -12960,10 +13185,13 @@
         <v>37</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA80" s="1"/>
+      <c r="AA80" s="1">
+        <f t="shared" si="24"/>
+        <v>0.81120000000000003</v>
+      </c>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
@@ -13022,7 +13250,7 @@
         <v>21</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-2</v>
       </c>
       <c r="M81" s="1"/>
@@ -13031,21 +13259,21 @@
         <v>0</v>
       </c>
       <c r="P81" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.8</v>
       </c>
       <c r="Q81" s="5"/>
       <c r="R81" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S81" s="17"/>
       <c r="T81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>40.526315789473685</v>
       </c>
       <c r="U81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.526315789473685</v>
       </c>
       <c r="V81" s="1">
@@ -13061,10 +13289,13 @@
         <v>37</v>
       </c>
       <c r="Z81" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA81" s="1"/>
+      <c r="AA81" s="1">
+        <f t="shared" si="24"/>
+        <v>1.2349999999999999</v>
+      </c>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
@@ -13123,7 +13354,7 @@
         <v>90</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-12</v>
       </c>
       <c r="M82" s="1"/>
@@ -13132,15 +13363,15 @@
         <v>123</v>
       </c>
       <c r="P82" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.6</v>
       </c>
       <c r="Q82" s="5">
-        <f t="shared" ref="Q82:Q87" si="23">15*P82-O82-F82</f>
+        <f t="shared" ref="Q82:Q87" si="25">15*P82-O82-F82</f>
         <v>40</v>
       </c>
       <c r="R82" s="5">
-        <f t="shared" ref="R82:R87" si="24">S82</f>
+        <f t="shared" ref="R82:R87" si="26">S82</f>
         <v>100</v>
       </c>
       <c r="S82" s="17">
@@ -13148,11 +13379,11 @@
         <v>100</v>
       </c>
       <c r="T82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18.846153846153847</v>
       </c>
       <c r="U82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.435897435897436</v>
       </c>
       <c r="V82" s="1">
@@ -13166,10 +13397,13 @@
       </c>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
-      <c r="AA82" s="1"/>
+      <c r="AA82" s="1">
+        <f t="shared" si="24"/>
+        <v>1.8719999999999999</v>
+      </c>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
@@ -13226,7 +13460,7 @@
         <v>81</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-22</v>
       </c>
       <c r="M83" s="1"/>
@@ -13235,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.8</v>
       </c>
       <c r="Q83" s="5">
@@ -13250,11 +13484,11 @@
         <v>200</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18.220338983050848</v>
       </c>
       <c r="U83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.9661016949152539</v>
       </c>
       <c r="V83" s="1">
@@ -13268,10 +13502,13 @@
       </c>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27</v>
       </c>
-      <c r="AA83" s="1"/>
+      <c r="AA83" s="1">
+        <f t="shared" si="24"/>
+        <v>1.77</v>
+      </c>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
@@ -13330,7 +13567,7 @@
         <v>78</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-11</v>
       </c>
       <c r="M84" s="1"/>
@@ -13339,11 +13576,11 @@
         <v>38</v>
       </c>
       <c r="P84" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.4</v>
       </c>
       <c r="Q84" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>103</v>
       </c>
       <c r="R84" s="5">
@@ -13354,11 +13591,11 @@
         <v>200</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20.746268656716417</v>
       </c>
       <c r="U84" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.3134328358208958</v>
       </c>
       <c r="V84" s="1">
@@ -13372,10 +13609,13 @@
       </c>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27</v>
       </c>
-      <c r="AA84" s="1"/>
+      <c r="AA84" s="1">
+        <f t="shared" si="24"/>
+        <v>2.0099999999999998</v>
+      </c>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
@@ -13432,7 +13672,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-5</v>
       </c>
       <c r="M85" s="1"/>
@@ -13441,11 +13681,11 @@
         <v>64</v>
       </c>
       <c r="P85" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.2</v>
       </c>
       <c r="Q85" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>26</v>
       </c>
       <c r="R85" s="5">
@@ -13456,11 +13696,11 @@
         <v>50</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>17.258064516129032</v>
       </c>
       <c r="U85" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.806451612903226</v>
       </c>
       <c r="V85" s="1">
@@ -13474,10 +13714,13 @@
       </c>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.200000000000001</v>
       </c>
-      <c r="AA85" s="1"/>
+      <c r="AA85" s="1">
+        <f t="shared" si="24"/>
+        <v>2.0460000000000003</v>
+      </c>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
@@ -13534,7 +13777,7 @@
         <v>165</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-32</v>
       </c>
       <c r="M86" s="1"/>
@@ -13543,7 +13786,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26.6</v>
       </c>
       <c r="Q86" s="5">
@@ -13558,11 +13801,11 @@
         <v>400</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.308270676691729</v>
       </c>
       <c r="U86" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.15037593984962405</v>
       </c>
       <c r="V86" s="1">
@@ -13576,10 +13819,13 @@
       </c>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>52.5</v>
       </c>
-      <c r="AA86" s="1"/>
+      <c r="AA86" s="1">
+        <f t="shared" si="24"/>
+        <v>3.99</v>
+      </c>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
@@ -13638,7 +13884,7 @@
         <v>129</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-37</v>
       </c>
       <c r="M87" s="1"/>
@@ -13647,15 +13893,15 @@
         <v>0</v>
       </c>
       <c r="P87" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.399999999999999</v>
       </c>
       <c r="Q87" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="R87" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>150</v>
       </c>
       <c r="S87" s="17">
@@ -13663,11 +13909,11 @@
         <v>150</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18.913043478260871</v>
       </c>
       <c r="U87" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.760869565217392</v>
       </c>
       <c r="V87" s="1">
@@ -13683,10 +13929,13 @@
         <v>123</v>
       </c>
       <c r="Z87" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>61.499999999999993</v>
       </c>
-      <c r="AA87" s="1"/>
+      <c r="AA87" s="1">
+        <f t="shared" si="24"/>
+        <v>7.5439999999999987</v>
+      </c>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
@@ -13737,7 +13986,7 @@
       <c r="J88" s="10"/>
       <c r="K88" s="10"/>
       <c r="L88" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M88" s="10"/>
@@ -13746,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="P88" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q88" s="12"/>
@@ -13756,11 +14005,11 @@
         <v>50</v>
       </c>
       <c r="T88" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" s="10">
@@ -13774,10 +14023,13 @@
       </c>
       <c r="Y88" s="10"/>
       <c r="Z88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA88" s="1"/>
+      <c r="AA88" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
@@ -13836,7 +14088,7 @@
         <v>69</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-57</v>
       </c>
       <c r="M89" s="1"/>
@@ -13845,21 +14097,21 @@
         <v>227</v>
       </c>
       <c r="P89" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.4</v>
       </c>
       <c r="Q89" s="5"/>
       <c r="R89" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S89" s="17"/>
       <c r="T89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>114.16666666666667</v>
       </c>
       <c r="U89" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>114.16666666666667</v>
       </c>
       <c r="V89" s="1">
@@ -13873,10 +14125,13 @@
       </c>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA89" s="1"/>
+      <c r="AA89" s="1">
+        <f t="shared" si="24"/>
+        <v>0.624</v>
+      </c>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
@@ -13933,7 +14188,7 @@
         <v>14.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.24399999999999977</v>
       </c>
       <c r="M90" s="1"/>
@@ -13942,21 +14197,21 @@
         <v>88</v>
       </c>
       <c r="P90" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.9487999999999999</v>
       </c>
       <c r="Q90" s="5"/>
       <c r="R90" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S90" s="17"/>
       <c r="T90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>35.847802495930551</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>35.847802495930551</v>
       </c>
       <c r="V90" s="1">
@@ -13970,10 +14225,13 @@
       </c>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA90" s="1"/>
+      <c r="AA90" s="1">
+        <f t="shared" si="24"/>
+        <v>2.9487999999999999</v>
+      </c>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
@@ -14032,7 +14290,7 @@
         <v>64</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-14</v>
       </c>
       <c r="M91" s="1"/>
@@ -14041,21 +14299,21 @@
         <v>5</v>
       </c>
       <c r="P91" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q91" s="5"/>
       <c r="R91" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S91" s="17"/>
       <c r="T91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>17.899999999999999</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.899999999999999</v>
       </c>
       <c r="V91" s="1">
@@ -14069,10 +14327,13 @@
       </c>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA91" s="1"/>
+      <c r="AA91" s="1">
+        <f t="shared" si="24"/>
+        <v>3.1</v>
+      </c>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
@@ -14131,7 +14392,7 @@
         <v>13.3</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-3.2680000000000007</v>
       </c>
       <c r="M92" s="1"/>
@@ -14140,24 +14401,24 @@
         <v>0</v>
       </c>
       <c r="P92" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.0064000000000002</v>
       </c>
       <c r="Q92" s="5">
-        <f t="shared" ref="Q92:Q103" si="25">15*P92-O92-F92</f>
+        <f t="shared" ref="Q92:Q103" si="27">15*P92-O92-F92</f>
         <v>4.8200000000000038</v>
       </c>
       <c r="R92" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="S92" s="17"/>
       <c r="T92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.089712918660286</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.597687400318978</v>
       </c>
       <c r="V92" s="1">
@@ -14171,10 +14432,13 @@
       </c>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5</v>
       </c>
-      <c r="AA92" s="1"/>
+      <c r="AA92" s="1">
+        <f t="shared" si="24"/>
+        <v>2.0064000000000002</v>
+      </c>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
@@ -14233,7 +14497,7 @@
         <v>112</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-12</v>
       </c>
       <c r="M93" s="1"/>
@@ -14242,24 +14506,24 @@
         <v>132</v>
       </c>
       <c r="P93" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>20</v>
       </c>
       <c r="Q93" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>77</v>
       </c>
       <c r="R93" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>77</v>
       </c>
       <c r="S93" s="17"/>
       <c r="T93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="U93" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.15</v>
       </c>
       <c r="V93" s="1">
@@ -14273,10 +14537,13 @@
       </c>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>30.8</v>
       </c>
-      <c r="AA93" s="1"/>
+      <c r="AA93" s="1">
+        <f t="shared" si="24"/>
+        <v>8</v>
+      </c>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
@@ -14335,7 +14602,7 @@
         <v>54</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-23</v>
       </c>
       <c r="M94" s="1"/>
@@ -14344,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.2</v>
       </c>
       <c r="Q94" s="5">
@@ -14352,16 +14619,16 @@
         <v>46.600000000000009</v>
       </c>
       <c r="R94" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>47</v>
       </c>
       <c r="S94" s="17"/>
       <c r="T94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.064516129032258</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.4838709677419351</v>
       </c>
       <c r="V94" s="1">
@@ -14375,10 +14642,13 @@
       </c>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.45</v>
       </c>
-      <c r="AA94" s="1"/>
+      <c r="AA94" s="1">
+        <f t="shared" si="24"/>
+        <v>2.17</v>
+      </c>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
@@ -14435,7 +14705,7 @@
         <v>13.7</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.53200000000000003</v>
       </c>
       <c r="M95" s="1"/>
@@ -14444,21 +14714,21 @@
         <v>0</v>
       </c>
       <c r="P95" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.8464</v>
       </c>
       <c r="Q95" s="5"/>
       <c r="R95" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S95" s="17"/>
       <c r="T95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30.134204609331086</v>
       </c>
       <c r="U95" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30.134204609331086</v>
       </c>
       <c r="V95" s="1">
@@ -14474,10 +14744,13 @@
         <v>37</v>
       </c>
       <c r="Z95" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA95" s="1"/>
+      <c r="AA95" s="1">
+        <f t="shared" si="24"/>
+        <v>2.8464</v>
+      </c>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
@@ -14534,7 +14807,7 @@
         <v>10.78</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.10700000000000109</v>
       </c>
       <c r="M96" s="1"/>
@@ -14543,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="P96" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.1774</v>
       </c>
       <c r="Q96" s="5">
@@ -14551,16 +14824,16 @@
         <v>16.434200000000001</v>
       </c>
       <c r="R96" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>16</v>
       </c>
       <c r="S96" s="17"/>
       <c r="T96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12.800587857077248</v>
       </c>
       <c r="U96" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.4523743914760727</v>
       </c>
       <c r="V96" s="1">
@@ -14574,10 +14847,13 @@
       </c>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16</v>
       </c>
-      <c r="AA96" s="1"/>
+      <c r="AA96" s="1">
+        <f t="shared" si="24"/>
+        <v>2.1774</v>
+      </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
@@ -14636,7 +14912,7 @@
         <v>87</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-25</v>
       </c>
       <c r="M97" s="1"/>
@@ -14645,24 +14921,24 @@
         <v>110</v>
       </c>
       <c r="P97" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.4</v>
       </c>
       <c r="Q97" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17</v>
       </c>
       <c r="R97" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17</v>
       </c>
       <c r="S97" s="17"/>
       <c r="T97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="U97" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.629032258064516</v>
       </c>
       <c r="V97" s="1">
@@ -14676,10 +14952,13 @@
       </c>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.61</v>
       </c>
-      <c r="AA97" s="1"/>
+      <c r="AA97" s="1">
+        <f t="shared" si="24"/>
+        <v>4.0920000000000005</v>
+      </c>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
@@ -14738,7 +15017,7 @@
         <v>81</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-53</v>
       </c>
       <c r="M98" s="1"/>
@@ -14747,21 +15026,21 @@
         <v>333</v>
       </c>
       <c r="P98" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.6</v>
       </c>
       <c r="Q98" s="5"/>
       <c r="R98" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S98" s="17"/>
       <c r="T98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>61.071428571428577</v>
       </c>
       <c r="U98" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>61.071428571428577</v>
       </c>
       <c r="V98" s="1">
@@ -14775,10 +15054,13 @@
       </c>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA98" s="1"/>
+      <c r="AA98" s="1">
+        <f t="shared" si="24"/>
+        <v>0.55999999999999994</v>
+      </c>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
@@ -14829,7 +15111,7 @@
         <v>181</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-181</v>
       </c>
       <c r="M99" s="1"/>
@@ -14838,21 +15120,21 @@
         <v>372</v>
       </c>
       <c r="P99" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q99" s="5"/>
       <c r="R99" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S99" s="17"/>
       <c r="T99" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U99" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V99" s="1">
@@ -14866,10 +15148,13 @@
       </c>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA99" s="1"/>
+      <c r="AA99" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
@@ -14926,7 +15211,7 @@
         <v>295</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-295</v>
       </c>
       <c r="M100" s="1"/>
@@ -14935,21 +15220,21 @@
         <v>0</v>
       </c>
       <c r="P100" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q100" s="5"/>
       <c r="R100" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S100" s="17"/>
       <c r="T100" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U100" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V100" s="1">
@@ -14963,10 +15248,13 @@
       </c>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA100" s="1"/>
+      <c r="AA100" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
@@ -15019,7 +15307,7 @@
         <v>5</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-6</v>
       </c>
       <c r="M101" s="1"/>
@@ -15028,7 +15316,7 @@
         <v>25</v>
       </c>
       <c r="P101" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.2</v>
       </c>
       <c r="Q101" s="5"/>
@@ -15040,11 +15328,11 @@
         <v>200</v>
       </c>
       <c r="T101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-475</v>
       </c>
       <c r="U101" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-125</v>
       </c>
       <c r="V101" s="1">
@@ -15060,10 +15348,13 @@
         <v>139</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
-      <c r="AA101" s="1"/>
+      <c r="AA101" s="1">
+        <f t="shared" si="24"/>
+        <v>-2.0000000000000004E-2</v>
+      </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
@@ -15116,7 +15407,7 @@
         <v>5</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L106" si="26">E102-K102</f>
+        <f t="shared" ref="L102:L106" si="28">E102-K102</f>
         <v>-6</v>
       </c>
       <c r="M102" s="1"/>
@@ -15125,7 +15416,7 @@
         <v>30</v>
       </c>
       <c r="P102" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.2</v>
       </c>
       <c r="Q102" s="5"/>
@@ -15137,11 +15428,11 @@
         <v>200</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-500</v>
       </c>
       <c r="U102" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-150</v>
       </c>
       <c r="V102" s="1">
@@ -15157,10 +15448,13 @@
         <v>141</v>
       </c>
       <c r="Z102" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
-      <c r="AA102" s="1"/>
+      <c r="AA102" s="1">
+        <f t="shared" si="24"/>
+        <v>-2.0000000000000004E-2</v>
+      </c>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
@@ -15219,7 +15513,7 @@
         <v>51</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-9</v>
       </c>
       <c r="M103" s="1"/>
@@ -15228,15 +15522,15 @@
         <v>0</v>
       </c>
       <c r="P103" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.4</v>
       </c>
       <c r="Q103" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>16</v>
       </c>
       <c r="R103" s="5">
-        <f t="shared" ref="R101:R104" si="27">S103</f>
+        <f t="shared" ref="R103" si="29">S103</f>
         <v>60</v>
       </c>
       <c r="S103" s="17">
@@ -15244,11 +15538,11 @@
         <v>60</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>20.238095238095237</v>
       </c>
       <c r="U103" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.095238095238095</v>
       </c>
       <c r="V103" s="1">
@@ -15262,10 +15556,13 @@
       </c>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18</v>
       </c>
-      <c r="AA103" s="1"/>
+      <c r="AA103" s="1">
+        <f t="shared" si="24"/>
+        <v>2.52</v>
+      </c>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
@@ -15324,7 +15621,7 @@
         <v>31</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="M104" s="1"/>
@@ -15333,7 +15630,7 @@
         <v>80</v>
       </c>
       <c r="P104" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.8</v>
       </c>
       <c r="Q104" s="5"/>
@@ -15345,11 +15642,11 @@
         <v>150</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>28.27586206896552</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.206896551724139</v>
       </c>
       <c r="V104" s="1">
@@ -15365,10 +15662,13 @@
         <v>143</v>
       </c>
       <c r="Z104" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
-      <c r="AA104" s="1"/>
+      <c r="AA104" s="1">
+        <f t="shared" si="24"/>
+        <v>1.74</v>
+      </c>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
@@ -15417,7 +15717,7 @@
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
       <c r="L105" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M105" s="10"/>
@@ -15426,21 +15726,21 @@
         <v>0</v>
       </c>
       <c r="P105" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q105" s="12"/>
       <c r="R105" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S105" s="17"/>
       <c r="T105" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" s="10">
@@ -15456,10 +15756,13 @@
         <v>101</v>
       </c>
       <c r="Z105" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA105" s="1"/>
+      <c r="AA105" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
@@ -15508,7 +15811,7 @@
         <v>2</v>
       </c>
       <c r="L106" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="M106" s="10"/>
@@ -15517,21 +15820,21 @@
         <v>0</v>
       </c>
       <c r="P106" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Q106" s="12"/>
       <c r="R106" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="S106" s="17"/>
       <c r="T106" s="1" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" s="10">
@@ -15547,10 +15850,13 @@
         <v>101</v>
       </c>
       <c r="Z106" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AA106" s="1"/>
+      <c r="AA106" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
